--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -894,10 +894,10 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33</v>
+        <v>7.96</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.67</v>
+        <v>-0.04</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>3.57</v>
+        <v>8.94</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.43</v>
+        <v>-0.06</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6</v>
+        <v>9.58</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.4</v>
+        <v>0.58</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>37.71</v>
+        <v>42.34</v>
       </c>
       <c r="D2" t="n">
-        <v>-26.29</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="3">
@@ -2290,10 +2290,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>54.32</v>
+        <v>59.69</v>
       </c>
       <c r="D3" t="n">
-        <v>-17.68</v>
+        <v>-12.31</v>
       </c>
     </row>
     <row r="4">
@@ -2306,10 +2306,10 @@
         <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>69.04000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.96</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="5">

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62</v>
+        <v>310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.02</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.98</v>
+        <v>0.79</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>312</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66</v>
+        <v>314</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>3.98</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.02</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>4.88</v>
+        <v>8.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.12</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.98</v>
+        <v>8.16</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.02</v>
+        <v>0.16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69</v>
+        <v>317</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>7.68</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.9</v>
+        <v>-0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>318</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>319</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>8.82</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.43</v>
+        <v>0.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73</v>
+        <v>321</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>496</v>
+        <v>322</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.68</v>
+        <v>8.43</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.32</v>
+        <v>0.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,21 +950,31 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>497</v>
+        <v>323</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -980,21 +990,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>498</v>
+        <v>324</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1010,34 +1020,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>499</v>
+        <v>325</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1050,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>500</v>
+        <v>326</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.95</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,19 +1080,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>501</v>
+        <v>327</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1111,13 +1101,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>8.960000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,19 +1120,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>502</v>
+        <v>328</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1151,13 +1141,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>3.03</v>
+        <v>5.17</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.97</v>
+        <v>-2.83</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,19 +1160,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>503</v>
+        <v>329</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1191,13 +1181,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>3.12</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6</v>
+        <v>-4.88</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>504</v>
+        <v>1457</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1208,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.68</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>505</v>
+        <v>1458</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>506</v>
+        <v>1459</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1278,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1300,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>507</v>
+        <v>1460</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1308,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1324,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,15 +1340,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>589</v>
+        <v>1461</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1374,10 +1364,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1380,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>590</v>
+        <v>1462</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1420,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>591</v>
+        <v>1463</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.83</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,15 +1460,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>592</v>
+        <v>1464</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1474,10 +1484,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0.25</v>
+        <v>-0.6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1500,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>593</v>
+        <v>1465</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1530,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>594</v>
+        <v>1466</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,15 +1560,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>595</v>
+        <v>1467</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1594,10 +1584,10 @@
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.130000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,15 +1600,15 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>596</v>
+        <v>1468</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1624,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.25</v>
+        <v>8.94</v>
       </c>
       <c r="H33" t="n">
-        <v>0.25</v>
+        <v>-0.06</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1640,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>597</v>
+        <v>1469</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,24 +1680,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>598</v>
+        <v>1470</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1710,15 +1720,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>599</v>
+        <v>1471</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1734,10 +1744,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>10.14</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1.14</v>
+        <v>0.03</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,34 +1760,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>600</v>
+        <v>1472</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>9.58</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,34 +1790,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>806</v>
+        <v>1473</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1830,24 +1820,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>807</v>
+        <v>1474</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,24 +1860,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>808</v>
+        <v>1475</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1890,34 +1900,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>809</v>
+        <v>1476</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>8.52</v>
+        <v>3.38</v>
       </c>
       <c r="H41" t="n">
-        <v>0.02</v>
+        <v>-5.62</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1930,34 +1940,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>810</v>
+        <v>1674</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>8.539999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1970,34 +1980,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>811</v>
+        <v>1675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,34 +2010,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>812</v>
+        <v>1676</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2050,34 +2040,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>813</v>
+        <v>1677</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>8.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="H45" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2090,24 +2080,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>814</v>
+        <v>1678</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,24 +2120,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>815</v>
+        <v>1679</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2150,34 +2160,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>816</v>
+        <v>1680</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>8.279999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.22</v>
+        <v>0.13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2190,41 +2200,1221 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>817</v>
+        <v>1681</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2387</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2388</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2389</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2390</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2391</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2392</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2393</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2395</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2396</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2397</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2398</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F73" t="n">
         <v>8.5</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G73" t="n">
         <v>8.52</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H73" t="n">
         <v>0.02</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2399</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2401</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2405</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2406</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8621</v>
       </c>
     </row>
@@ -2271,13 +3461,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>42.34</v>
+        <v>106.09</v>
       </c>
       <c r="D2" t="n">
-        <v>-21.66</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="3">
@@ -2287,13 +3477,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C3" t="n">
-        <v>59.69</v>
+        <v>120.08</v>
       </c>
       <c r="D3" t="n">
-        <v>-12.31</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="4">
@@ -2303,13 +3493,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C4" t="n">
-        <v>75.02</v>
+        <v>125.84</v>
       </c>
       <c r="D4" t="n">
-        <v>3.02</v>
+        <v>-0.1600000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +3509,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C5" t="n">
-        <v>59.45</v>
+        <v>106.91</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.550000000000001</v>
+        <v>-12.09</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>310</v>
+        <v>62</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>8.789999999999999</v>
+        <v>5.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0.79</v>
+        <v>-2.98</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>311</v>
+        <v>63</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>312</v>
+        <v>64</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>313</v>
+        <v>65</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>314</v>
+        <v>66</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.130000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13</v>
+        <v>-4.02</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>315</v>
+        <v>67</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.1</v>
+        <v>4.88</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>-3.12</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>316</v>
+        <v>68</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>8.16</v>
+        <v>3.98</v>
       </c>
       <c r="H8" t="n">
-        <v>0.16</v>
+        <v>-4.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>317</v>
+        <v>69</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.68</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.32</v>
+        <v>-4.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>318</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>319</v>
+        <v>71</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>320</v>
+        <v>72</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.82</v>
+        <v>5.57</v>
       </c>
       <c r="H12" t="n">
-        <v>0.82</v>
+        <v>-2.43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>321</v>
+        <v>73</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>322</v>
+        <v>496</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.43</v>
+        <v>8.68</v>
       </c>
       <c r="H14" t="n">
-        <v>0.43</v>
+        <v>-0.32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,31 +950,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>323</v>
+        <v>497</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -990,21 +980,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>324</v>
+        <v>498</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46157</v>
+        <v>46145</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1020,24 +1010,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>325</v>
+        <v>499</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46158</v>
+        <v>46146</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,24 +1050,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>326</v>
+        <v>500</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46159</v>
+        <v>46147</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-5.95</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1080,19 +1090,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>327</v>
+        <v>501</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1101,13 +1111,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>7.88</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1120,19 +1130,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>328</v>
+        <v>502</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1141,13 +1151,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.17</v>
+        <v>3.03</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.83</v>
+        <v>-5.97</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1160,19 +1170,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>329</v>
+        <v>503</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARMAS, MARIO C [0206]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1181,13 +1191,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>3.12</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.88</v>
+        <v>-0.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1200,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1457</v>
+        <v>504</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1208,26 +1218,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>8.68</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1458</v>
+        <v>505</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1459</v>
+        <v>506</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,16 +1278,26 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1300,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1460</v>
+        <v>507</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1308,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1324,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1340,15 +1350,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1364,10 +1374,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>8.92</v>
+        <v>9.08</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1380,34 +1390,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1462</v>
+        <v>590</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>8.960000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,34 +1420,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1463</v>
+        <v>591</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>8.83</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1460,15 +1450,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1464</v>
+        <v>592</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1484,10 +1474,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.4</v>
+        <v>9.25</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1500,24 +1490,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1465</v>
+        <v>593</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,24 +1530,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1466</v>
+        <v>594</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1560,15 +1570,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1467</v>
+        <v>595</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1584,10 +1594,10 @@
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.699999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7</v>
+        <v>0.13</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1600,15 +1610,15 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1468</v>
+        <v>596</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1624,10 +1634,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>8.94</v>
+        <v>9.25</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1640,34 +1650,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1469</v>
+        <v>597</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>9.029999999999999</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,34 +1680,24 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1470</v>
+        <v>598</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1720,15 +1710,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1471</v>
+        <v>599</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1744,10 +1734,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.029999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03</v>
+        <v>1.14</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,24 +1750,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1472</v>
+        <v>600</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46154</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.58</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,24 +1790,34 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1473</v>
+        <v>806</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46143</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1820,34 +1830,24 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1474</v>
+        <v>807</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,34 +1860,24 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1475</v>
+        <v>808</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1900,34 +1890,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1476</v>
+        <v>809</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>3.38</v>
+        <v>8.52</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.62</v>
+        <v>0.02</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1940,34 +1930,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1674</v>
+        <v>810</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G42" t="n">
-        <v>9.08</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1980,24 +1970,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1675</v>
+        <v>811</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,24 +2010,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1676</v>
+        <v>812</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2040,34 +2050,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1677</v>
+        <v>813</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G45" t="n">
-        <v>9.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2080,34 +2090,24 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1678</v>
+        <v>814</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,34 +2120,24 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1679</v>
+        <v>815</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2160,34 +2150,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1680</v>
+        <v>816</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G48" t="n">
-        <v>9.130000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.13</v>
+        <v>-0.22</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2200,34 +2190,34 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1681</v>
+        <v>817</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>9.25</v>
+        <v>8.52</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2235,1186 +2225,6 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1682</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>1683</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1684</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>9</v>
-      </c>
-      <c r="G52" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1685</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>9</v>
-      </c>
-      <c r="G53" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1686</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>9</v>
-      </c>
-      <c r="G54" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1687</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>9</v>
-      </c>
-      <c r="G55" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>1688</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>9</v>
-      </c>
-      <c r="G56" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>1689</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1690</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>1691</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>9</v>
-      </c>
-      <c r="G59" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>1692</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>9</v>
-      </c>
-      <c r="G60" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>1693</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>LAO, ANDREW S [3881]</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>2387</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>2388</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>2389</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>46145</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>2390</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>2391</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>2392</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>2393</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G68" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>2394</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G69" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>2395</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>2396</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2397</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>2398</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G73" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>2399</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G74" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>2400</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G75" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>2401</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>2402</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>2403</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2404</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2405</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>8621</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2406</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>OSUNA, MICHAEL [0661]</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
         <v>8621</v>
       </c>
     </row>
@@ -3461,13 +2271,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>106.09</v>
+        <v>42.34</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.91</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="3">
@@ -3477,13 +2287,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>120.08</v>
+        <v>59.69</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.92</v>
+        <v>-12.31</v>
       </c>
     </row>
     <row r="4">
@@ -3493,13 +2303,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>125.84</v>
+        <v>75.02</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1600000000000001</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="5">
@@ -3509,13 +2319,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>106.91</v>
+        <v>59.45</v>
       </c>
       <c r="D5" t="n">
-        <v>-12.09</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62</v>
+        <v>310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.02</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.98</v>
+        <v>0.79</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>312</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66</v>
+        <v>314</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>3.98</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.02</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>4.88</v>
+        <v>8.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.12</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.98</v>
+        <v>8.16</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.02</v>
+        <v>0.16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69</v>
+        <v>317</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>7.68</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.9</v>
+        <v>-0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>318</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>319</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>8.82</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.43</v>
+        <v>0.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73</v>
+        <v>321</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,19 +910,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>496</v>
+        <v>322</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.68</v>
+        <v>8.43</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.32</v>
+        <v>0.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,21 +950,31 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>497</v>
+        <v>323</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -980,21 +990,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>498</v>
+        <v>324</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1010,34 +1020,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>499</v>
+        <v>325</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1050,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>500</v>
+        <v>326</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.95</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,19 +1080,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>501</v>
+        <v>327</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1111,13 +1101,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>8.960000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,19 +1120,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>502</v>
+        <v>328</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1151,13 +1141,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>3.03</v>
+        <v>5.17</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.97</v>
+        <v>-2.83</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,19 +1160,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>503</v>
+        <v>329</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1191,13 +1181,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>8.07</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>504</v>
+        <v>1457</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1208,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.68</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>505</v>
+        <v>1458</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>506</v>
+        <v>1459</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1278,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1300,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>507</v>
+        <v>1460</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1308,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1324,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,15 +1340,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>589</v>
+        <v>1461</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1374,10 +1364,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1380,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>590</v>
+        <v>1462</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1420,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>591</v>
+        <v>1463</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.83</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,15 +1460,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>592</v>
+        <v>1464</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1474,10 +1484,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0.25</v>
+        <v>-0.6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1500,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>593</v>
+        <v>1465</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1530,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>594</v>
+        <v>1466</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,15 +1560,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>595</v>
+        <v>1467</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1594,10 +1584,10 @@
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.130000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,15 +1600,15 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>596</v>
+        <v>1468</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1624,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.25</v>
+        <v>8.94</v>
       </c>
       <c r="H33" t="n">
-        <v>0.25</v>
+        <v>-0.06</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1640,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>597</v>
+        <v>1469</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,24 +1680,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>598</v>
+        <v>1470</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1710,15 +1720,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>599</v>
+        <v>1471</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1734,10 +1744,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>10.14</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1.14</v>
+        <v>0.03</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,34 +1760,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>600</v>
+        <v>1472</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>9.58</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,34 +1790,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>806</v>
+        <v>1473</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1830,24 +1820,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>807</v>
+        <v>1474</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,24 +1860,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>808</v>
+        <v>1475</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1890,34 +1900,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>809</v>
+        <v>1476</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>8.52</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1930,34 +1940,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>810</v>
+        <v>1674</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>8.539999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1970,34 +1980,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>811</v>
+        <v>1675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,34 +2010,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>812</v>
+        <v>1676</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2050,34 +2040,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>813</v>
+        <v>1677</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>8.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="H45" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2090,24 +2080,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>814</v>
+        <v>1678</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,24 +2120,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>815</v>
+        <v>1679</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9.27</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2150,34 +2160,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>816</v>
+        <v>1680</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>8.279999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.22</v>
+        <v>0.13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2190,41 +2200,1221 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>817</v>
+        <v>1681</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2387</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2388</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2389</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2390</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2391</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2392</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2393</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2395</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2396</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2397</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2398</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F73" t="n">
         <v>8.5</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G73" t="n">
         <v>8.52</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H73" t="n">
         <v>0.02</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2399</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2401</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2405</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2406</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8621</v>
       </c>
     </row>
@@ -2271,13 +3461,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>42.34</v>
+        <v>111.04</v>
       </c>
       <c r="D2" t="n">
-        <v>-21.66</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="3">
@@ -2287,13 +3477,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C3" t="n">
-        <v>59.69</v>
+        <v>125.66</v>
       </c>
       <c r="D3" t="n">
-        <v>-12.31</v>
+        <v>-0.3400000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2303,13 +3493,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C4" t="n">
-        <v>75.02</v>
+        <v>130.67</v>
       </c>
       <c r="D4" t="n">
-        <v>3.02</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +3509,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C5" t="n">
-        <v>59.45</v>
+        <v>110.63</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,19 +1200,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1457</v>
+        <v>330</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.68</v>
+        <v>4.02</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.32</v>
+        <v>-3.98</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,16 +1248,26 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.68</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,7 +1288,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1300,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1308,26 +1318,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>8.960000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.17</v>
+        <v>-0.04</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.4</v>
+        <v>8.83</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6</v>
+        <v>-0.17</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1508,16 +1508,26 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46150</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,7 +1540,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1538,7 +1548,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1560,7 +1570,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1568,26 +1578,16 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>8.94</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.06</v>
+        <v>0.7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>9.029999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>8.93</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.029999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1768,16 +1768,26 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46157</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,7 +1800,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1798,7 +1808,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1820,7 +1830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1828,26 +1838,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>9.300000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>8.960000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1940,15 +1940,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1674</v>
+        <v>1476</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>9.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1980,24 +1980,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1675</v>
+        <v>1477</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-5.9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,7 +2020,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2018,16 +2028,26 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46143</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>9.08</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2040,7 +2060,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2048,26 +2068,16 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2080,7 +2090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2088,26 +2098,16 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="H47" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>9.130000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="H48" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>9.25</v>
+        <v>9.27</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2248,16 +2248,26 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46151</v>
+        <v>46149</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2270,7 +2280,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2278,16 +2288,26 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46152</v>
+        <v>46150</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2300,7 +2320,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2308,26 +2328,16 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F52" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>10.14</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2340,7 +2350,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2348,26 +2358,16 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F53" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>9.58</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>9.23</v>
+        <v>10.14</v>
       </c>
       <c r="H54" t="n">
-        <v>0.23</v>
+        <v>1.14</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>9.050000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="H55" t="n">
-        <v>0.05</v>
+        <v>0.58</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>9.550000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="H56" t="n">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2508,16 +2508,26 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46158</v>
+        <v>46156</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2530,7 +2540,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2538,16 +2548,26 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46159</v>
+        <v>46157</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2560,7 +2580,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2568,26 +2588,16 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.34</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2600,7 +2610,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2608,26 +2618,16 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>9.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>9.199999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2680,34 +2680,34 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2387</v>
+        <v>1692</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>-8.5</v>
+        <v>0.28</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2720,24 +2720,34 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2388</v>
+        <v>1693</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46144</v>
+        <v>46162</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2750,24 +2760,34 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2389</v>
+        <v>1694</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46145</v>
+        <v>46163</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-4.45</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2780,7 +2800,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2788,7 +2808,7 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2804,10 +2824,10 @@
         <v>8.5</v>
       </c>
       <c r="G65" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.02</v>
+        <v>-8.5</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2820,7 +2840,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2828,26 +2848,16 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F66" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2860,7 +2870,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2868,26 +2878,16 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F67" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         <v>8.5</v>
       </c>
       <c r="G68" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
       <c r="H68" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>8.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.529999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2988,16 +2988,26 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46151</v>
+        <v>46148</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3010,7 +3020,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3018,16 +3028,26 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46152</v>
+        <v>46149</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3040,7 +3060,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3048,7 +3068,7 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3064,10 +3084,10 @@
         <v>8.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.279999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.22</v>
+        <v>0.03</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3080,7 +3100,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3088,26 +3108,16 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F73" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3120,7 +3130,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3128,26 +3138,16 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F74" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>8.5</v>
       </c>
       <c r="G75" t="n">
-        <v>8.529999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
         <v>8.5</v>
       </c>
       <c r="G76" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="H76" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3248,16 +3248,26 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46158</v>
+        <v>46155</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3270,7 +3280,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3278,16 +3288,26 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46159</v>
+        <v>46156</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3300,7 +3320,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2404</v>
+        <v>2401</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3308,7 +3328,7 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3340,7 +3360,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3348,26 +3368,16 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F80" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3380,41 +3390,191 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2405</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>2406</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C84" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F81" t="n">
+      <c r="F84" t="n">
         <v>8.5</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G84" t="n">
         <v>8.57</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2407</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
         <v>8621</v>
       </c>
     </row>
@@ -3461,13 +3621,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C2" t="n">
-        <v>111.04</v>
+        <v>115.06</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.96</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="3">
@@ -3477,13 +3637,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>125.66</v>
+        <v>128.76</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3400000000000001</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="4">
@@ -3493,13 +3653,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C4" t="n">
-        <v>130.67</v>
+        <v>135.22</v>
       </c>
       <c r="D4" t="n">
-        <v>4.67</v>
+        <v>0.2199999999999998</v>
       </c>
     </row>
     <row r="5">
@@ -3509,13 +3669,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119</v>
+        <v>127.5</v>
       </c>
       <c r="C5" t="n">
-        <v>110.63</v>
+        <v>115.26</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.369999999999999</v>
+        <v>-12.24</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -1224,10 +1224,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>4.02</v>
+        <v>7.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.98</v>
+        <v>-0.1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>3.1</v>
+        <v>8.32</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.9</v>
+        <v>-0.68</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>4.55</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.45</v>
+        <v>-0.53</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         <v>8.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.63</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>-3.87</v>
+        <v>0.03</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
         <v>120</v>
       </c>
       <c r="C2" t="n">
-        <v>115.06</v>
+        <v>118.94</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.94</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="3">
@@ -3640,10 +3640,10 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>128.76</v>
+        <v>133.98</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.24</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="4">
@@ -3656,10 +3656,10 @@
         <v>135</v>
       </c>
       <c r="C4" t="n">
-        <v>135.22</v>
+        <v>139.14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2199999999999998</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="5">
@@ -3672,10 +3672,10 @@
         <v>127.5</v>
       </c>
       <c r="C5" t="n">
-        <v>115.26</v>
+        <v>119.16</v>
       </c>
       <c r="D5" t="n">
-        <v>-12.24</v>
+        <v>-8.34</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,19 +1240,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1457</v>
+        <v>331</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46143</v>
+        <v>46164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.68</v>
+        <v>7.68</v>
       </c>
       <c r="H23" t="n">
         <v>-0.32</v>
@@ -1280,15 +1280,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1458</v>
+        <v>332</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1310,15 +1310,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1459</v>
+        <v>333</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46145</v>
+        <v>46166</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1340,19 +1340,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1460</v>
+        <v>334</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1380,19 +1380,19 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1461</v>
+        <v>335</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>8.92</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.08</v>
+        <v>0.28</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,19 +1420,19 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1462</v>
+        <v>336</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>8.960000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.04</v>
+        <v>-2.9</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1460,19 +1460,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1463</v>
+        <v>337</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HERNANDEZ, KEVIN [6712]</t>
+          <t>ARMAS, MARIO C [0206]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>8.83</v>
+        <v>3.88</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.17</v>
+        <v>-4.12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1464</v>
+        <v>1426</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6</v>
+        <v>-0.32</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1465</v>
+        <v>1427</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46151</v>
+        <v>46144</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1466</v>
+        <v>1428</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1467</v>
+        <v>1429</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.699999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1468</v>
+        <v>1430</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1469</v>
+        <v>1431</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>9.029999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1470</v>
+        <v>1432</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>8.93</v>
+        <v>8.83</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1471</v>
+        <v>1433</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>9.029999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H37" t="n">
-        <v>0.03</v>
+        <v>-0.6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1472</v>
+        <v>1434</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46158</v>
+        <v>46151</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1473</v>
+        <v>1435</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46159</v>
+        <v>46152</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1474</v>
+        <v>1436</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>9.050000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1475</v>
+        <v>1437</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>9.300000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3</v>
+        <v>-0.06</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1476</v>
+        <v>1438</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>8.960000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1477</v>
+        <v>1439</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>8.32</v>
+        <v>8.93</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2020,15 +2020,15 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1674</v>
+        <v>1440</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>9.08</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2060,15 +2060,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1675</v>
+        <v>1441</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2090,15 +2090,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1676</v>
+        <v>1442</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2120,15 +2120,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1677</v>
+        <v>1443</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>9.25</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2160,15 +2160,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1678</v>
+        <v>1444</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2200,15 +2200,15 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1679</v>
+        <v>1445</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>9.27</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2240,15 +2240,15 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1680</v>
+        <v>1446</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>9.130000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="H50" t="n">
-        <v>0.13</v>
+        <v>-0.68</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2280,15 +2280,15 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1681</v>
+        <v>1447</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>9.25</v>
+        <v>8.74</v>
       </c>
       <c r="H51" t="n">
-        <v>0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2320,15 +2320,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1682</v>
+        <v>1448</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2350,15 +2350,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1683</v>
+        <v>1449</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2380,15 +2380,15 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1684</v>
+        <v>1450</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>10.14</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.14</v>
+        <v>-9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2420,15 +2420,15 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1685</v>
+        <v>1451</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>9.58</v>
+        <v>9.42</v>
       </c>
       <c r="H55" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2460,15 +2460,15 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1686</v>
+        <v>1452</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>9.23</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2500,15 +2500,15 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1687</v>
+        <v>1453</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LAO, ANDREW S [3881]</t>
+          <t>HERNANDEZ, KEVIN [6712]</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>9.050000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="H57" t="n">
-        <v>0.05</v>
+        <v>-5.95</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1688</v>
+        <v>1643</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>9.550000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="H58" t="n">
-        <v>0.55</v>
+        <v>0.08</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1689</v>
+        <v>1644</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46158</v>
+        <v>46144</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1690</v>
+        <v>1645</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46159</v>
+        <v>46145</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1691</v>
+        <v>1646</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>9.34</v>
+        <v>9.25</v>
       </c>
       <c r="H61" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1692</v>
+        <v>1647</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
         <v>9</v>
       </c>
       <c r="G62" t="n">
-        <v>9.279999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="H62" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1693</v>
+        <v>1648</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46162</v>
+        <v>46148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1694</v>
+        <v>1649</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>8.470000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.53</v>
+        <v>0.13</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2800,34 +2800,34 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2387</v>
+        <v>1650</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="H65" t="n">
-        <v>-8.5</v>
+        <v>0.25</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2840,15 +2840,15 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2388</v>
+        <v>1651</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2870,15 +2870,15 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2389</v>
+        <v>1652</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2900,34 +2900,34 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2390</v>
+        <v>1653</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G68" t="n">
-        <v>8.52</v>
+        <v>10.14</v>
       </c>
       <c r="H68" t="n">
-        <v>0.02</v>
+        <v>1.14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2391</v>
+        <v>1654</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
-        <v>8.539999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="H69" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2980,34 +2980,34 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2392</v>
+        <v>1655</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G70" t="n">
-        <v>8.550000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="H70" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3020,34 +3020,34 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2393</v>
+        <v>1656</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
-        <v>8.51</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3060,34 +3060,34 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2394</v>
+        <v>1657</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
-        <v>8.529999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3100,15 +3100,15 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2395</v>
+        <v>1658</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3130,15 +3130,15 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2396</v>
+        <v>1659</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3160,34 +3160,34 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2397</v>
+        <v>1660</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
-        <v>8.279999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.22</v>
+        <v>0.34</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2398</v>
+        <v>1661</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G76" t="n">
-        <v>8.52</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3240,34 +3240,34 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2399</v>
+        <v>1662</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
-        <v>8.529999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3280,34 +3280,34 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2400</v>
+        <v>1663</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>8.529999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>0.03</v>
+        <v>-0.53</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3320,34 +3320,34 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2401</v>
+        <v>1664</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>8.550000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.05</v>
+        <v>0.53</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3360,15 +3360,15 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2402</v>
+        <v>1665</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3390,15 +3390,15 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2403</v>
+        <v>1666</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3420,34 +3420,34 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2404</v>
+        <v>1667</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.05</v>
+        <v>-9</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3460,34 +3460,34 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2405</v>
+        <v>1668</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G83" t="n">
-        <v>8.449999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.05</v>
+        <v>0.62</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3500,34 +3500,34 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2406</v>
+        <v>1669</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OSUNA, MICHAEL [0661]</t>
+          <t>LAO, ANDREW S [3881]</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
-        <v>8.57</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3540,41 +3540,1081 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2407</v>
+        <v>1670</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>LAO, ANDREW S [3881]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2356</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>OSUNA, MICHAEL [0661]</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C86" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2357</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2358</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2359</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2360</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2361</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2362</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2363</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2364</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2365</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2366</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2367</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2368</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2369</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2370</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2371</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2372</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2373</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2375</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2376</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F106" t="n">
         <v>8.5</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G106" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H106" t="n">
         <v>0.03</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>TIRE WEB</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2377</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2378</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2379</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2380</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2381</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2382</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>8621</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2383</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OSUNA, MICHAEL [0661]</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>TIRE WEB</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
         <v>8621</v>
       </c>
     </row>
@@ -3621,13 +4661,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="C2" t="n">
-        <v>118.94</v>
+        <v>143.88</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.06</v>
+        <v>-16.12</v>
       </c>
     </row>
     <row r="3">
@@ -3637,13 +4677,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>133.98</v>
+        <v>164.22</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.02</v>
+        <v>-15.78</v>
       </c>
     </row>
     <row r="4">
@@ -3653,13 +4693,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C4" t="n">
-        <v>139.14</v>
+        <v>172.55</v>
       </c>
       <c r="D4" t="n">
-        <v>4.14</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="5">
@@ -3669,13 +4709,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.5</v>
+        <v>170</v>
       </c>
       <c r="C5" t="n">
-        <v>119.16</v>
+        <v>149.56</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.34</v>
+        <v>-20.44</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -1484,10 +1484,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>3.88</v>
+        <v>7.85</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.12</v>
+        <v>-0.15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>3.05</v>
+        <v>8.82</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.95</v>
+        <v>-0.18</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         <v>8.5</v>
       </c>
       <c r="G113" t="n">
-        <v>4.72</v>
+        <v>8.57</v>
       </c>
       <c r="H113" t="n">
-        <v>-3.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         <v>160</v>
       </c>
       <c r="C2" t="n">
-        <v>143.88</v>
+        <v>147.85</v>
       </c>
       <c r="D2" t="n">
-        <v>-16.12</v>
+        <v>-12.15</v>
       </c>
     </row>
     <row r="3">
@@ -4680,10 +4680,10 @@
         <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>164.22</v>
+        <v>169.99</v>
       </c>
       <c r="D3" t="n">
-        <v>-15.78</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="4">
@@ -4712,10 +4712,10 @@
         <v>170</v>
       </c>
       <c r="C5" t="n">
-        <v>149.56</v>
+        <v>153.41</v>
       </c>
       <c r="D5" t="n">
-        <v>-20.44</v>
+        <v>-16.59</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8621.xlsx
+++ b/sheet/8621.xlsx
@@ -3564,10 +3564,10 @@
         <v>9</v>
       </c>
       <c r="G85" t="n">
-        <v>4.63</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.37</v>
+        <v>0.28</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>180</v>
       </c>
       <c r="C4" t="n">
-        <v>172.55</v>
+        <v>177.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-7.45</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="5">
